--- a/Data/Temp/Fiscal_Calander.xlsx
+++ b/Data/Temp/Fiscal_Calander.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aws-svc-rpa52d\Documents\UiPath\3043_LATAM_DataLoad\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aws-svc-rpa52d\Documents\UiPath\3043_LATAM_DataLoad\Data\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03F3D23E-6FE1-463F-8E4B-FC4173360611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ED4BC3-9BA7-46C5-BE24-7F5ECEC86915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
-  <si>
-    <t>Status</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
   <si>
     <t>MonitoringStart_Date</t>
   </si>
@@ -79,6 +76,12 @@
   </si>
   <si>
     <t>Active</t>
+  </si>
+  <si>
+    <t>RevenueStatus</t>
+  </si>
+  <si>
+    <t>InvoiceStatus</t>
   </si>
 </sst>
 </file>
@@ -431,33 +434,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="15.7109375" customWidth="1"/>
     <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="5" max="5" width="17.28515625" customWidth="1"/>
     <col min="7" max="8" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
       </c>
       <c r="B2" s="3">
         <v>46055</v>
@@ -466,12 +473,15 @@
         <v>46058</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" s="3">
         <v>46083</v>
@@ -480,12 +490,15 @@
         <v>46086</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3">
         <v>46111</v>
@@ -494,12 +507,15 @@
         <v>46114</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3">
         <v>46146</v>
@@ -508,12 +524,15 @@
         <v>46149</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3">
         <v>46174</v>
@@ -522,12 +541,15 @@
         <v>46177</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="3">
         <v>46202</v>
@@ -536,12 +558,15 @@
         <v>46205</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" s="3">
         <v>46237</v>
@@ -550,12 +575,15 @@
         <v>46240</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3">
         <v>46265</v>
@@ -564,12 +592,15 @@
         <v>46268</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10" s="3">
         <v>46293</v>
@@ -578,12 +609,15 @@
         <v>46296</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="3">
         <v>46328</v>
@@ -592,12 +626,15 @@
         <v>46331</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="3">
         <v>46356</v>
@@ -606,12 +643,15 @@
         <v>46359</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="3">
         <v>46391</v>
@@ -620,7 +660,10 @@
         <v>46394</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Temp/Fiscal_Calander.xlsx
+++ b/Data/Temp/Fiscal_Calander.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aws-svc-rpa52d\Documents\UiPath\3043_LATAM_DataLoad\Data\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7ED4BC3-9BA7-46C5-BE24-7F5ECEC86915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0291AA-9452-46E8-8083-F46401FF9CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -467,7 +467,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="3">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="C2" s="3">
         <v>46058</v>
@@ -484,7 +484,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="3">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="C3" s="3">
         <v>46086</v>
@@ -501,7 +501,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="3">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="C4" s="3">
         <v>46114</v>
@@ -518,16 +518,16 @@
         <v>6</v>
       </c>
       <c r="B5" s="3">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="C5" s="3">
         <v>46149</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -535,16 +535,16 @@
         <v>7</v>
       </c>
       <c r="B6" s="3">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="C6" s="3">
         <v>46177</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -552,16 +552,16 @@
         <v>8</v>
       </c>
       <c r="B7" s="3">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="C7" s="3">
-        <v>46205</v>
+        <v>46255</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -569,7 +569,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="3">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="C8" s="3">
         <v>46240</v>
@@ -586,7 +586,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="3">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="C9" s="3">
         <v>46268</v>
@@ -603,7 +603,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="3">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C10" s="3">
         <v>46296</v>
@@ -620,7 +620,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="3">
-        <v>46328</v>
+        <v>46329</v>
       </c>
       <c r="C11" s="3">
         <v>46331</v>
@@ -637,7 +637,7 @@
         <v>13</v>
       </c>
       <c r="B12" s="3">
-        <v>46356</v>
+        <v>46357</v>
       </c>
       <c r="C12" s="3">
         <v>46359</v>
@@ -654,7 +654,7 @@
         <v>14</v>
       </c>
       <c r="B13" s="3">
-        <v>46391</v>
+        <v>46392</v>
       </c>
       <c r="C13" s="3">
         <v>46394</v>

--- a/Data/Temp/Fiscal_Calander.xlsx
+++ b/Data/Temp/Fiscal_Calander.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aws-svc-rpa52d\Documents\UiPath\3043_LATAM_DataLoad\Data\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C0291AA-9452-46E8-8083-F46401FF9CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD91BD79-6170-4C3E-B3BC-BB814A74E43C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LATAM_2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="19">
   <si>
     <t>MonitoringStart_Date</t>
   </si>
@@ -555,7 +556,7 @@
         <v>46203</v>
       </c>
       <c r="C7" s="3">
-        <v>46255</v>
+        <v>46205</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
@@ -586,10 +587,10 @@
         <v>10</v>
       </c>
       <c r="B9" s="3">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="C9" s="3">
-        <v>46268</v>
+        <v>46264</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>16</v>
@@ -670,4 +671,242 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBC2E586-9BEA-4B86-8AB1-6FD8BFC564AD}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.28515625" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" customWidth="1"/>
+    <col min="5" max="5" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3">
+        <v>46056</v>
+      </c>
+      <c r="C2" s="3">
+        <v>46058</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="3">
+        <v>46084</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46086</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="3">
+        <v>46112</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46114</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="3">
+        <v>46147</v>
+      </c>
+      <c r="C5" s="3">
+        <v>46149</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3">
+        <v>46175</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46177</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="3">
+        <v>46203</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46255</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>46238</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46240</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="3">
+        <v>46266</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46268</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="3">
+        <v>46294</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46296</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46329</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46331</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46357</v>
+      </c>
+      <c r="C12" s="3">
+        <v>46359</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46392</v>
+      </c>
+      <c r="C13" s="3">
+        <v>46394</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>